--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1047,6 +1047,262 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125996432</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102004</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ekgetingbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Xylotrechus antilope</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schönherr, 1817)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>fälla</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Alsterån 2, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>580427</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6315698</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125996434</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12339</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100841</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Orangefläckig brunbagge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dircaea australis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fairmaire, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>fälla</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Alsterån 2, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>580427</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6315698</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Mönsterås kommuns eklandskap</t>
         </is>

--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,6 +1303,390 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126160433</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5224</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101582</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bredbandad ekbarkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Plagionotus detritus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>fälla</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Alsterån 2, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>580427</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6315698</v>
+      </c>
+      <c r="S7" t="n">
+        <v>14</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126160437</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5285</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102147</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spindelbock</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Aegomorphus clavipes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schrank, 1781)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>fälla</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Alsterån 2, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>580427</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6315698</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126159635</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5287</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102320</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lindbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Oplosia cinerea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Mulsant, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>fälla</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Alsterån 1, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>580585</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6315580</v>
+      </c>
+      <c r="S9" t="n">
+        <v>24</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Mönsterås kommuns eklandskap</t>
         </is>

--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>125713013</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1687,6 +1687,385 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126290301</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57810</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Alsterån 2, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>580427</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6315698</v>
+      </c>
+      <c r="S10" t="n">
+        <v>14</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joakim Holm, Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126290298</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5276</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100975</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ekgrenbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Exocentrus adspersus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Mulsant, 1846</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>bankning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Alsterån 2, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>580427</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6315698</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Holm, Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126290300</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8274</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101592</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ekcylinderbagge</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platypus cylindrus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>fälla</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Alsterån 2, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>580427</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6315698</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joakim Holm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joakim Holm, Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Mönsterås kommuns eklandskap</t>
         </is>

--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,7 +806,7 @@
         <v>125713013</v>
       </c>
       <c r="B3" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>126290301</v>
       </c>
       <c r="B10" t="n">
-        <v>57810</v>
+        <v>57814</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2066,6 +2066,138 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126341668</v>
+      </c>
+      <c r="B13" t="n">
+        <v>40072</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101871</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ekglasvinge</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Synanthedon vespiformis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1761)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>pheromone</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Strömsfors, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>580449</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6315656</v>
+      </c>
+      <c r="S13" t="n">
+        <v>13</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Mönsterås kommuns eklandskap</t>
         </is>

--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,10 +1694,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126290301</v>
+        <v>126290298</v>
       </c>
       <c r="B10" t="n">
-        <v>57814</v>
+        <v>5276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,36 +1705,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103020</v>
+        <v>100975</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ekgrenbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Exocentrus adspersus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Mulsant, 1846</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>bankning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Alsterån 2, Sm</t>
@@ -1817,10 +1822,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126290298</v>
+        <v>126290301</v>
       </c>
       <c r="B11" t="n">
-        <v>5276</v>
+        <v>57814</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,41 +1833,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100975</v>
+        <v>103020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekgrenbock</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Exocentrus adspersus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Mulsant, 1846</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>bankning</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Alsterån 2, Sm</t>
@@ -2198,6 +2198,535 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126373581</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8274</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101592</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ekcylinderbagge</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platypus cylindrus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>fälla</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Alsterån 1, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>580585</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6315580</v>
+      </c>
+      <c r="S14" t="n">
+        <v>24</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126375645</v>
+      </c>
+      <c r="B15" t="n">
+        <v>9395</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100859</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bokoxe</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dorcus parallelipipedus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Strömsfors, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>580341</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6315819</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126372998</v>
+      </c>
+      <c r="B16" t="n">
+        <v>40068</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>pheromone</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Strömsfors, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>580446</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6315650</v>
+      </c>
+      <c r="S16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126374818</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5254</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>101424</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gulröd blankbock</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Obrium cantharinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Strömsfors, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>580507</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6315661</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På GROT-hög, sprang på grenar av asp.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
         <is>
           <t>Mönsterås kommuns eklandskap</t>
         </is>

--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2731,6 +2731,391 @@
           <t>Mönsterås kommuns eklandskap</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126388763</v>
+      </c>
+      <c r="B18" t="n">
+        <v>12848</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100701</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Colydium elongatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Strömsfors, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>580483</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6315697</v>
+      </c>
+      <c r="S18" t="n">
+        <v>21</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126388086</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5276</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100975</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ekgrenbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Exocentrus adspersus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Mulsant, 1846</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Strömsfors, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>580483</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6315697</v>
+      </c>
+      <c r="S19" t="n">
+        <v>21</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126386117</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56602</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Strömsfors, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>580474</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6315550</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Oscar Nordahl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -2597,32 +2597,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126374818</v>
+        <v>126388763</v>
       </c>
       <c r="B17" t="n">
-        <v>5254</v>
+        <v>12848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101424</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Gulröd blankbock</t>
-        </is>
+        <v>100701</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Obrium cantharinum</t>
+          <t>Colydium elongatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2644,7 +2639,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2653,13 +2648,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580507</v>
+        <v>580483</v>
       </c>
       <c r="R17" t="n">
-        <v>6315661</v>
+        <v>6315697</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2688,22 +2683,17 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På GROT-hög, sprang på grenar av asp.</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2712,6 +2702,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2734,32 +2725,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126388763</v>
+        <v>126388086</v>
       </c>
       <c r="B18" t="n">
-        <v>12848</v>
+        <v>5276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100701</v>
+        <v>100975</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ekgrenbock</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Colydium elongatum</t>
+          <t>Exocentrus adspersus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Mulsant, 1846</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2771,7 +2767,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2862,69 +2858,65 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126388086</v>
+        <v>126386117</v>
       </c>
       <c r="B19" t="n">
-        <v>5276</v>
+        <v>56602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100975</v>
+        <v>100088</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ekgrenbock</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Exocentrus adspersus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Mulsant, 1846</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Strömsfors, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580483</v>
+        <v>580474</v>
       </c>
       <c r="R19" t="n">
-        <v>6315697</v>
+        <v>6315550</v>
       </c>
       <c r="S19" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2948,12 +2940,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2963,7 +2955,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2972,7 +2964,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2987,18 +2978,14 @@
           <t>Oscar Nordahl</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Mönsterås kommuns eklandskap</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126386117</v>
+        <v>126374818</v>
       </c>
       <c r="B20" t="n">
-        <v>56602</v>
+        <v>5254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3006,21 +2993,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100088</v>
+        <v>101424</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Gulröd blankbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Obrium cantharinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3031,29 +3018,33 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Strömsfors, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580474</v>
+        <v>580507</v>
       </c>
       <c r="R20" t="n">
-        <v>6315550</v>
+        <v>6315661</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3077,22 +3068,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På GROT-hög, sprang på grenar av asp.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3115,7 +3111,11 @@
           <t>Oscar Nordahl</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -1694,10 +1694,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126290298</v>
+        <v>126290301</v>
       </c>
       <c r="B10" t="n">
-        <v>5276</v>
+        <v>57814</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,41 +1705,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100975</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ekgrenbock</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Exocentrus adspersus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Mulsant, 1846</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>bankning</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Alsterån 2, Sm</t>
@@ -1822,10 +1817,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126290301</v>
+        <v>126290298</v>
       </c>
       <c r="B11" t="n">
-        <v>57814</v>
+        <v>5276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,36 +1828,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>100975</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ekgrenbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Exocentrus adspersus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Mulsant, 1846</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>bankning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Alsterån 2, Sm</t>
@@ -2205,32 +2205,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126373581</v>
+        <v>126375645</v>
       </c>
       <c r="B14" t="n">
-        <v>8274</v>
+        <v>9395</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101592</v>
+        <v>100859</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ekcylinderbagge</t>
+          <t>Bokoxe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platypus cylindrus</t>
+          <t>Dorcus parallelipipedus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2239,7 +2239,11 @@
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
@@ -2248,22 +2252,22 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Alsterån 1, Sm</t>
+          <t>Strömsfors, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580585</v>
+        <v>580341</v>
       </c>
       <c r="R14" t="n">
-        <v>6315580</v>
+        <v>6315819</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2292,7 +2296,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2302,7 +2306,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2333,32 +2337,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126375645</v>
+        <v>126373581</v>
       </c>
       <c r="B15" t="n">
-        <v>9395</v>
+        <v>8274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100859</v>
+        <v>101592</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bokoxe</t>
+          <t>Ekcylinderbagge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dorcus parallelipipedus</t>
+          <t>Platypus cylindrus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1792)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2367,11 +2371,7 @@
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
@@ -2380,22 +2380,22 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strömsfors, Sm</t>
+          <t>Alsterån 1, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580341</v>
+        <v>580585</v>
       </c>
       <c r="R15" t="n">
-        <v>6315819</v>
+        <v>6315580</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2597,27 +2597,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126388763</v>
+        <v>126386117</v>
       </c>
       <c r="B17" t="n">
-        <v>12848</v>
+        <v>56602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100701</v>
+        <v>100088</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Colydium elongatum</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2628,33 +2633,29 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strömsfors, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580483</v>
+        <v>580474</v>
       </c>
       <c r="R17" t="n">
-        <v>6315697</v>
+        <v>6315550</v>
       </c>
       <c r="S17" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2678,12 +2679,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2693,7 +2694,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2702,7 +2703,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2717,45 +2717,41 @@
           <t>Oscar Nordahl</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Mönsterås kommuns eklandskap</t>
-        </is>
-      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126388086</v>
+        <v>126374818</v>
       </c>
       <c r="B18" t="n">
-        <v>5276</v>
+        <v>5254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100975</v>
+        <v>101424</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ekgrenbock</t>
+          <t>Gulröd blankbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Exocentrus adspersus</t>
+          <t>Obrium cantharinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Mulsant, 1846</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2767,12 +2763,12 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>frispringande/krypande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>lampa</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2781,13 +2777,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580483</v>
+        <v>580507</v>
       </c>
       <c r="R18" t="n">
-        <v>6315697</v>
+        <v>6315661</v>
       </c>
       <c r="S18" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2816,17 +2812,22 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På GROT-hög, sprang på grenar av asp.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2835,7 +2836,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2858,32 +2858,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126386117</v>
+        <v>126388763</v>
       </c>
       <c r="B19" t="n">
-        <v>56602</v>
+        <v>12848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100088</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Vanlig snok</t>
-        </is>
+        <v>100701</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Colydium elongatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2894,29 +2889,33 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Strömsfors, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580474</v>
+        <v>580483</v>
       </c>
       <c r="R19" t="n">
-        <v>6315550</v>
+        <v>6315697</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2940,22 +2939,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>elongatum/noblecourti</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2964,6 +2968,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2978,41 +2983,45 @@
           <t>Oscar Nordahl</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Mönsterås kommuns eklandskap</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126374818</v>
+        <v>126388086</v>
       </c>
       <c r="B20" t="n">
-        <v>5254</v>
+        <v>5276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101424</v>
+        <v>100975</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gulröd blankbock</t>
+          <t>Ekgrenbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Obrium cantharinum</t>
+          <t>Exocentrus adspersus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Mulsant, 1846</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -3024,12 +3033,12 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3038,13 +3047,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580507</v>
+        <v>580483</v>
       </c>
       <c r="R20" t="n">
-        <v>6315661</v>
+        <v>6315697</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3073,22 +3082,17 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På GROT-hög, sprang på grenar av asp.</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3097,6 +3101,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -1694,10 +1694,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126290301</v>
+        <v>126290298</v>
       </c>
       <c r="B10" t="n">
-        <v>57814</v>
+        <v>5276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,36 +1705,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103020</v>
+        <v>100975</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ekgrenbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Exocentrus adspersus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Mulsant, 1846</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>bankning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Alsterån 2, Sm</t>
@@ -1817,10 +1822,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126290298</v>
+        <v>126290301</v>
       </c>
       <c r="B11" t="n">
-        <v>5276</v>
+        <v>57815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,41 +1833,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100975</v>
+        <v>103020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ekgrenbock</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Exocentrus adspersus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Mulsant, 1846</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>bankning</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Alsterån 2, Sm</t>
@@ -2076,7 +2076,7 @@
         <v>126341668</v>
       </c>
       <c r="B13" t="n">
-        <v>40072</v>
+        <v>40073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>126372998</v>
       </c>
       <c r="B16" t="n">
-        <v>40068</v>
+        <v>40069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>126386117</v>
       </c>
       <c r="B17" t="n">
-        <v>56602</v>
+        <v>56603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -2205,32 +2205,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126375645</v>
+        <v>126373581</v>
       </c>
       <c r="B14" t="n">
-        <v>9395</v>
+        <v>8274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100859</v>
+        <v>101592</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bokoxe</t>
+          <t>Ekcylinderbagge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dorcus parallelipipedus</t>
+          <t>Platypus cylindrus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1792)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2239,11 +2239,7 @@
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
@@ -2252,22 +2248,22 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Strömsfors, Sm</t>
+          <t>Alsterån 1, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580341</v>
+        <v>580585</v>
       </c>
       <c r="R14" t="n">
-        <v>6315819</v>
+        <v>6315580</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2296,7 +2292,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2306,7 +2302,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2337,32 +2333,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126373581</v>
+        <v>126375645</v>
       </c>
       <c r="B15" t="n">
-        <v>8274</v>
+        <v>9395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101592</v>
+        <v>100859</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ekcylinderbagge</t>
+          <t>Bokoxe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platypus cylindrus</t>
+          <t>Dorcus parallelipipedus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2371,7 +2367,11 @@
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
@@ -2380,22 +2380,22 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Alsterån 1, Sm</t>
+          <t>Strömsfors, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580585</v>
+        <v>580341</v>
       </c>
       <c r="R15" t="n">
-        <v>6315580</v>
+        <v>6315819</v>
       </c>
       <c r="S15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 34721-2024 artfynd.xlsx
+++ b/artfynd/A 34721-2024 artfynd.xlsx
@@ -2205,32 +2205,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126373581</v>
+        <v>126375645</v>
       </c>
       <c r="B14" t="n">
-        <v>8274</v>
+        <v>9395</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101592</v>
+        <v>100859</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ekcylinderbagge</t>
+          <t>Bokoxe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platypus cylindrus</t>
+          <t>Dorcus parallelipipedus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2239,7 +2239,11 @@
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
@@ -2248,22 +2252,22 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Alsterån 1, Sm</t>
+          <t>Strömsfors, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580585</v>
+        <v>580341</v>
       </c>
       <c r="R14" t="n">
-        <v>6315580</v>
+        <v>6315819</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2292,7 +2296,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2302,7 +2306,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2333,32 +2337,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126375645</v>
+        <v>126373581</v>
       </c>
       <c r="B15" t="n">
-        <v>9395</v>
+        <v>8274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100859</v>
+        <v>101592</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bokoxe</t>
+          <t>Ekcylinderbagge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dorcus parallelipipedus</t>
+          <t>Platypus cylindrus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1792)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2367,11 +2371,7 @@
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
@@ -2380,22 +2380,22 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strömsfors, Sm</t>
+          <t>Alsterån 1, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580341</v>
+        <v>580585</v>
       </c>
       <c r="R15" t="n">
-        <v>6315819</v>
+        <v>6315580</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
